--- a/maintenance_forms/009_maintenance_audit_for_operators--maintenance_forms.xlsx
+++ b/maintenance_forms/009_maintenance_audit_for_operators--maintenance_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1167,7 +1167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>equipment</t>
+          <t>tool</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Equipment</t>
+          <t>Tool</t>
         </is>
       </c>
     </row>
@@ -1268,29 +1268,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>tool</t>
+          <t>system</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tool</t>
+          <t>System</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>equipment_type_choices</t>
+          <t>equipment_status_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>system</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>available</t>
+          <t>maintenance_required</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Maintenance Required</t>
         </is>
       </c>
     </row>
@@ -1319,29 +1319,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>maintenance_required</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Maintenance Required</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>equipment_status_choices</t>
+          <t>operator_name_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>user_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>User 1</t>
         </is>
       </c>
     </row>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>user_1</t>
+          <t>user_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>User 1</t>
+          <t>User 2</t>
         </is>
       </c>
     </row>
@@ -1370,29 +1370,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>user_2</t>
+          <t>user_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>User 2</t>
+          <t>User 3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>operator_name_choices</t>
+          <t>maintenance_frequency_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>user_3</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>User 3</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1438,12 +1438,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1455,29 +1455,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>quarterly</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Quarterly</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>maintenance_frequency_choices</t>
+          <t>equipment_status_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yearly</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yearly</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>available</t>
+          <t>maintenance_required</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Maintenance Required</t>
         </is>
       </c>
     </row>
@@ -1506,29 +1506,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>maintenance_required</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Maintenance Required</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>equipment_status_2_choices</t>
+          <t>operator_name_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>user_1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>User 1</t>
         </is>
       </c>
     </row>
@@ -1540,12 +1540,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>user_1</t>
+          <t>user_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>User 1</t>
+          <t>User 2</t>
         </is>
       </c>
     </row>
@@ -1557,29 +1557,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>user_2</t>
+          <t>user_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>User 2</t>
+          <t>User 3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>operator_name_2_choices</t>
+          <t>review_status_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>user_3</t>
+          <t>review_in_progress</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>User 3</t>
+          <t>Review In Progress</t>
         </is>
       </c>
     </row>
@@ -1591,27 +1591,10 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>review_in_progress</t>
+          <t>review_complete</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
-        <is>
-          <t>Review In Progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>review_status_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>review_complete</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
         <is>
           <t>Review Complete</t>
         </is>
